--- a/excels/demo_gears_3d (3).xlsx
+++ b/excels/demo_gears_3d (3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radin\Documents\Adi Heavy\Siraal\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E4F502-8C65-451E-86D1-739A44B272A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63BFAA1-BC17-4055-BDF2-EE1644ACFE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="144">
   <si>
     <t>SIRAAL 3D GEAR ENGINE — GEAR BILL OF MATERIALS</t>
   </si>
@@ -475,19 +475,7 @@
     <t>Power transmission shaft with keyway</t>
   </si>
   <si>
-    <t>Structural 90-degree mounting bracket</t>
-  </si>
-  <si>
-    <t>Custom_Motor_Mount</t>
-  </si>
-  <si>
-    <t>Our-Custom-part</t>
-  </si>
-  <si>
-    <t>Custom_Sensor_Pocket_Mount</t>
-  </si>
-  <si>
-    <t>Custom-Sensor</t>
+    <t>low</t>
   </si>
 </sst>
 </file>
@@ -938,6 +926,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -953,12 +947,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1242,44 +1230,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="31.5" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
     </row>
     <row r="2" spans="1:15" ht="18" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="68" t="s">
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
     </row>
     <row r="3" spans="1:15" ht="27.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1357,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
@@ -1455,7 +1443,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="61" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="K6" s="61" t="s">
         <v>22</v>
@@ -1509,80 +1497,32 @@
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" thickBot="1">
-      <c r="A8" s="61">
-        <v>5</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="61">
-        <v>60</v>
-      </c>
-      <c r="F8" s="61">
-        <v>40</v>
-      </c>
-      <c r="G8" s="61">
-        <v>20</v>
-      </c>
-      <c r="H8" s="63">
-        <v>25</v>
-      </c>
-      <c r="I8" s="61">
-        <v>1</v>
-      </c>
-      <c r="J8" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="63" t="s">
-        <v>143</v>
-      </c>
+      <c r="A8" s="61"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="63"/>
       <c r="M8" s="5"/>
       <c r="N8" s="6"/>
       <c r="O8" s="7"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" thickBot="1">
-      <c r="A9" s="65">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="65">
-        <v>120</v>
-      </c>
-      <c r="F9" s="65">
-        <v>120</v>
-      </c>
-      <c r="G9" s="65">
-        <v>15</v>
-      </c>
-      <c r="H9" s="65">
-        <v>50</v>
-      </c>
-      <c r="I9" s="65">
-        <v>1</v>
-      </c>
-      <c r="J9" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="65" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9" s="65"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
       <c r="M9" s="11"/>
       <c r="N9" s="12"/>
       <c r="O9" s="13"/>
@@ -1590,11 +1530,11 @@
     <row r="10" spans="1:15" ht="18" customHeight="1" thickBot="1">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="73"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="67"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -1839,20 +1779,20 @@
       <c r="O24" s="40"/>
     </row>
     <row r="25" spans="1:15" ht="21.75" customHeight="1">
-      <c r="A25" s="70" t="s">
+      <c r="A25" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="67"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="69"/>
       <c r="M25" s="43">
         <f>SUM(M4:M24)</f>
         <v>9.9999999999999985E-3</v>
@@ -1905,16 +1845,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2121,16 +2061,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2347,16 +2287,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="22.35" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -2537,14 +2477,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
